--- a/data/trans_dic/P55$privada-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P55$privada-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,11</t>
+          <t>0,0; 64,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,9</t>
+          <t>0,0; 72,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,96</t>
+          <t>0,0; 63,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,06; 50,19</t>
+          <t>12,21; 49,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,77; 79,07</t>
+          <t>23,81; 77,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,03; 100,0</t>
+          <t>14,88; 88,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,56; 57,46</t>
+          <t>12,15; 56,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,7; 63,25</t>
+          <t>22,61; 65,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,9; 71,09</t>
+          <t>9,53; 71,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,7; 71,36</t>
+          <t>15,18; 74,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,02; 46,14</t>
+          <t>15,77; 44,49</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,35</t>
+          <t>0,0; 56,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,11</t>
+          <t>0,0; 62,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,05</t>
+          <t>0,0; 49,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 38,78</t>
+          <t>6,99; 39,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,72</t>
+          <t>0,0; 72,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,53; 83,25</t>
+          <t>14,54; 82,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 29,44</t>
+          <t>3,67; 30,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 54,99</t>
+          <t>6,6; 55,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 54,76</t>
+          <t>6,18; 52,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 52,81</t>
+          <t>10,96; 53,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 29,44</t>
+          <t>8,68; 29,8</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,07</t>
+          <t>0,0; 30,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,45</t>
+          <t>0,0; 27,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,74; 54,63</t>
+          <t>10,55; 51,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 32,06</t>
+          <t>7,27; 31,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,94; 78,59</t>
+          <t>12,62; 77,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 40,65</t>
+          <t>5,35; 41,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,16</t>
+          <t>0,0; 48,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 30,38</t>
+          <t>6,57; 29,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 37,2</t>
+          <t>4,49; 36,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 25,3</t>
+          <t>4,66; 26,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 40,54</t>
+          <t>10,32; 40,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,46; 25,59</t>
+          <t>9,4; 25,75</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 21,88</t>
+          <t>6,55; 22,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,92; 26,67</t>
+          <t>7,96; 27,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 22,21</t>
+          <t>4,16; 23,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,99; 20,89</t>
+          <t>8,37; 21,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,84</t>
+          <t>0,0; 23,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,84</t>
+          <t>0,0; 43,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 36,31</t>
+          <t>7,0; 38,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 26,08</t>
+          <t>9,52; 24,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 18,51</t>
+          <t>6,41; 18,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 25,07</t>
+          <t>8,94; 25,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,89; 24,11</t>
+          <t>7,08; 25,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 20,23</t>
+          <t>10,03; 20,99</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,48</t>
+          <t>0,0; 29,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 23,1</t>
+          <t>2,79; 23,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 21,62</t>
+          <t>4,1; 22,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,06; 28,72</t>
+          <t>6,36; 26,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,86; 43,04</t>
+          <t>12,57; 43,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 13,9</t>
+          <t>2,6; 14,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 23,6</t>
+          <t>4,32; 24,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,75; 21,6</t>
+          <t>10,66; 20,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,44; 32,36</t>
+          <t>9,88; 33,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 14,0</t>
+          <t>3,49; 13,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 18,26</t>
+          <t>5,61; 18,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,27; 20,16</t>
+          <t>11,16; 20,65</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,7; 25,76</t>
+          <t>12,0; 24,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,64; 28,23</t>
+          <t>13,58; 27,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,41; 21,04</t>
+          <t>7,74; 20,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,22; 26,98</t>
+          <t>16,56; 26,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,55; 25,74</t>
+          <t>12,34; 25,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,64; 28,23</t>
+          <t>13,58; 27,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,41; 21,04</t>
+          <t>7,74; 20,44</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,04; 25,81</t>
+          <t>16,21; 25,93</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,32; 18,22</t>
+          <t>7,09; 18,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,3; 20,25</t>
+          <t>8,83; 20,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,49; 21,58</t>
+          <t>9,42; 21,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,7; 20,92</t>
+          <t>11,71; 20,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,6; 27,85</t>
+          <t>16,67; 27,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,25; 21,82</t>
+          <t>11,87; 21,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,14; 20,99</t>
+          <t>11,17; 21,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,51; 21,9</t>
+          <t>15,47; 21,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,36; 22,51</t>
+          <t>14,56; 22,25</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,2; 19,56</t>
+          <t>12,34; 19,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,71; 19,14</t>
+          <t>11,7; 19,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,22; 20,21</t>
+          <t>15,14; 19,99</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6504</t>
+          <t>0; 6518</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6040</t>
+          <t>0; 6059</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4987</t>
+          <t>0; 4483</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1207; 6021</t>
+          <t>1465; 5898</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3311; 10569</t>
+          <t>3182; 10417</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1957,32 +1957,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1209; 8045</t>
+          <t>1197; 7135</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1740; 7963</t>
+          <t>1684; 7856</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5103; 14871</t>
+          <t>5315; 15298</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1038; 8289</t>
+          <t>1111; 8311</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2367; 10756</t>
+          <t>2288; 11200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4142; 11928</t>
+          <t>4076; 11502</t>
         </is>
       </c>
     </row>
@@ -2135,22 +2135,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6085</t>
+          <t>0; 6146</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5906</t>
+          <t>0; 5919</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5490</t>
+          <t>0; 5285</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1276; 6770</t>
+          <t>1220; 6961</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2160,37 +2160,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6405</t>
+          <t>0; 6418</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>975; 5587</t>
+          <t>976; 5564</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>503; 4038</t>
+          <t>503; 4140</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1179; 8881</t>
+          <t>1067; 8894</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1136; 10031</t>
+          <t>1132; 9703</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1949; 9224</t>
+          <t>1915; 9302</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2578; 9178</t>
+          <t>2707; 9289</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4878</t>
+          <t>0; 5537</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6707</t>
+          <t>0; 6718</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1770; 9005</t>
+          <t>1739; 8534</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1570; 6793</t>
+          <t>1540; 6605</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1077; 6539</t>
+          <t>1050; 6441</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1001; 7724</t>
+          <t>1016; 7853</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6709</t>
+          <t>0; 7945</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1473; 6435</t>
+          <t>1392; 6253</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1187; 9798</t>
+          <t>1182; 9493</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1954; 10989</t>
+          <t>2023; 11649</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2926; 13292</t>
+          <t>3382; 13235</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4008; 10840</t>
+          <t>3982; 10908</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4373; 15456</t>
+          <t>4625; 15952</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5372; 18079</t>
+          <t>5396; 18384</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1619; 8853</t>
+          <t>1658; 9510</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5755; 15050</t>
+          <t>6033; 15165</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6051</t>
+          <t>0; 5564</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 8718</t>
+          <t>0; 9164</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2189; 11921</t>
+          <t>2297; 12510</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3496; 10115</t>
+          <t>3692; 9636</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5795; 17412</t>
+          <t>6033; 17014</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7527; 22214</t>
+          <t>7920; 22944</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5733; 17525</t>
+          <t>5147; 18349</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11016; 22422</t>
+          <t>11114; 23261</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3615</t>
+          <t>0; 4711</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1000; 8324</t>
+          <t>1006; 8327</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1830; 10230</t>
+          <t>1943; 10701</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2122; 8635</t>
+          <t>1911; 7998</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4318; 15673</t>
+          <t>4578; 15869</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2087; 11618</t>
+          <t>2175; 12444</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2196; 12513</t>
+          <t>2289; 12923</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10017; 20135</t>
+          <t>9933; 19565</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4957; 16989</t>
+          <t>5188; 17657</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4184; 16741</t>
+          <t>4176; 16532</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5402; 18321</t>
+          <t>5635; 18096</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13896; 24845</t>
+          <t>13756; 25457</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 705</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 778</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16850; 37108</t>
+          <t>17285; 35985</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19513; 40391</t>
+          <t>19427; 39374</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10915; 30982</t>
+          <t>11403; 30104</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22865; 38049</t>
+          <t>23349; 37483</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18186; 37314</t>
+          <t>17884; 36287</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19513; 40391</t>
+          <t>19427; 39374</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10915; 30982</t>
+          <t>11403; 30104</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22964; 36946</t>
+          <t>23206; 37112</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9267; 23059</t>
+          <t>8978; 22788</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12129; 29601</t>
+          <t>12907; 30208</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11525; 26215</t>
+          <t>11444; 26023</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18119; 32396</t>
+          <t>18141; 32050</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38331; 64313</t>
+          <t>38499; 63705</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34134; 60772</t>
+          <t>33064; 60575</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29432; 55461</t>
+          <t>29514; 57463</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>49902; 70448</t>
+          <t>49767; 70622</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>51325; 80466</t>
+          <t>52046; 79541</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51822; 83066</t>
+          <t>52430; 82146</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45142; 73803</t>
+          <t>45109; 74663</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>72522; 96337</t>
+          <t>72159; 95296</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$privada-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P55$privada-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,26</t>
+          <t>0,0; 65,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,13</t>
+          <t>0,0; 72,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,79</t>
+          <t>0,0; 69,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,21; 49,17</t>
+          <t>10,51; 51,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,81; 77,93</t>
+          <t>22,75; 78,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,88; 88,69</t>
+          <t>15,15; 88,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,15; 56,69</t>
+          <t>12,09; 54,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,61; 65,07</t>
+          <t>21,51; 63,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 71,27</t>
+          <t>8,94; 71,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,18; 74,3</t>
+          <t>17,72; 73,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,77; 44,49</t>
+          <t>16,6; 48,52</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,91</t>
+          <t>0,0; 50,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,24</t>
+          <t>0,0; 61,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,15</t>
+          <t>0,0; 49,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 39,87</t>
+          <t>6,79; 37,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,87</t>
+          <t>0,0; 72,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,54; 82,91</t>
+          <t>14,67; 100,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 30,18</t>
+          <t>3,73; 31,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 55,07</t>
+          <t>6,93; 54,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 52,97</t>
+          <t>9,56; 58,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,96; 53,26</t>
+          <t>11,03; 52,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,68; 29,8</t>
+          <t>7,69; 27,82</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,73</t>
+          <t>0,0; 28,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,49</t>
+          <t>0,0; 26,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 51,78</t>
+          <t>10,65; 54,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 31,18</t>
+          <t>7,14; 32,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,62; 77,41</t>
+          <t>12,55; 77,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,35; 41,33</t>
+          <t>5,37; 41,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,75</t>
+          <t>0,0; 48,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 29,52</t>
+          <t>6,94; 29,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 36,04</t>
+          <t>4,35; 34,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 26,82</t>
+          <t>4,77; 25,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,32; 40,37</t>
+          <t>10,54; 40,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,4; 25,75</t>
+          <t>8,95; 25,55</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 22,59</t>
+          <t>7,18; 22,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,96; 27,12</t>
+          <t>8,19; 27,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 23,86</t>
+          <t>4,12; 23,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,37; 21,05</t>
+          <t>8,66; 22,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,76</t>
+          <t>0,0; 24,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,98</t>
+          <t>0,0; 44,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 38,11</t>
+          <t>6,98; 39,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,52; 24,85</t>
+          <t>9,51; 24,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,41; 18,09</t>
+          <t>6,7; 19,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 25,89</t>
+          <t>8,37; 24,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 25,24</t>
+          <t>7,06; 23,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 20,99</t>
+          <t>10,41; 20,49</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,3</t>
+          <t>0,0; 28,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 23,11</t>
+          <t>2,77; 20,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,1; 22,61</t>
+          <t>3,91; 23,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 26,6</t>
+          <t>7,05; 27,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,57; 43,58</t>
+          <t>12,34; 44,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 14,89</t>
+          <t>3,55; 15,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 24,37</t>
+          <t>4,05; 23,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,66; 20,99</t>
+          <t>10,47; 20,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,88; 33,64</t>
+          <t>8,71; 32,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 13,82</t>
+          <t>4,27; 14,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,61; 18,03</t>
+          <t>6,1; 18,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,16; 20,65</t>
+          <t>11,15; 20,15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,0; 24,98</t>
+          <t>12,98; 26,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,58; 27,52</t>
+          <t>13,58; 27,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,74; 20,44</t>
+          <t>7,37; 19,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,56; 26,58</t>
+          <t>16,79; 27,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,34; 25,03</t>
+          <t>12,3; 25,77</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,58; 27,52</t>
+          <t>13,58; 27,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,74; 20,44</t>
+          <t>7,37; 19,97</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,21; 25,93</t>
+          <t>16,29; 26,82</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,09; 18,0</t>
+          <t>7,1; 17,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,83; 20,67</t>
+          <t>8,83; 20,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,42; 21,43</t>
+          <t>9,13; 21,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,71; 20,69</t>
+          <t>11,36; 20,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,67; 27,59</t>
+          <t>16,56; 27,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,87; 21,75</t>
+          <t>12,3; 21,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,17; 21,75</t>
+          <t>11,34; 21,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,47; 21,95</t>
+          <t>15,25; 21,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,56; 22,25</t>
+          <t>14,77; 22,51</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,34; 19,34</t>
+          <t>12,26; 20,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,7; 19,36</t>
+          <t>11,63; 19,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,14; 19,99</t>
+          <t>15,14; 20,43</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7773</t>
         </is>
       </c>
     </row>
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6518</t>
+          <t>0; 6657</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6059</t>
+          <t>0; 6060</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4483</t>
+          <t>0; 4859</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1465; 5898</t>
+          <t>1314; 6441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3182; 10417</t>
+          <t>3042; 10508</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1957,32 +1957,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1197; 7135</t>
+          <t>1218; 7156</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1684; 7856</t>
+          <t>1813; 8241</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5315; 15298</t>
+          <t>5057; 14949</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1111; 8311</t>
+          <t>1042; 8302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2288; 11200</t>
+          <t>2671; 11072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4076; 11502</t>
+          <t>4564; 13338</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5349</t>
         </is>
       </c>
     </row>
@@ -2135,22 +2135,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6146</t>
+          <t>0; 5473</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5919</t>
+          <t>0; 5891</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5285</t>
+          <t>0; 5310</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1220; 6961</t>
+          <t>1274; 6982</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2160,37 +2160,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6418</t>
+          <t>0; 6367</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>976; 5564</t>
+          <t>985; 6711</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>503; 4140</t>
+          <t>579; 4828</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1067; 8894</t>
+          <t>1119; 8832</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1132; 9703</t>
+          <t>1752; 10797</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1915; 9302</t>
+          <t>1927; 9234</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2707; 9289</t>
+          <t>2636; 9540</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7538</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5537</t>
+          <t>0; 5117</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6718</t>
+          <t>0; 6364</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1739; 8534</t>
+          <t>1755; 8907</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1540; 6605</t>
+          <t>1628; 7377</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1050; 6441</t>
+          <t>1044; 6424</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1016; 7853</t>
+          <t>1021; 7829</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7945</t>
+          <t>0; 7938</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1392; 6253</t>
+          <t>1657; 7125</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1182; 9493</t>
+          <t>1147; 9179</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2023; 11649</t>
+          <t>2073; 11276</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3382; 13235</t>
+          <t>3455; 13139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3982; 10908</t>
+          <t>4176; 11924</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>17528</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4625; 15952</t>
+          <t>5068; 16164</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5396; 18384</t>
+          <t>5549; 18699</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1658; 9510</t>
+          <t>1641; 9222</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6033; 15165</t>
+          <t>6681; 17206</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5564</t>
+          <t>0; 5671</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 9164</t>
+          <t>0; 9186</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2297; 12510</t>
+          <t>2290; 12861</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3692; 9636</t>
+          <t>3979; 10331</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6033; 17014</t>
+          <t>6302; 18116</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7920; 22944</t>
+          <t>7416; 21937</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5147; 18349</t>
+          <t>5132; 17373</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11114; 23261</t>
+          <t>12390; 24383</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14166</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18587</t>
+          <t>20254</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4711</t>
+          <t>0; 4529</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1006; 8327</t>
+          <t>998; 7450</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1943; 10701</t>
+          <t>1850; 10933</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1911; 7998</t>
+          <t>2317; 9026</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4578; 15869</t>
+          <t>4493; 16023</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2175; 12444</t>
+          <t>2968; 12552</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2289; 12923</t>
+          <t>2147; 12697</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9933; 19565</t>
+          <t>10552; 20530</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5188; 17657</t>
+          <t>4570; 17302</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4176; 16532</t>
+          <t>5101; 16760</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5635; 18096</t>
+          <t>6121; 18670</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13756; 25457</t>
+          <t>14905; 26920</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>29528</t>
+          <t>32653</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>29528</t>
+          <t>32653</t>
         </is>
       </c>
     </row>
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17285; 35985</t>
+          <t>18694; 38635</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19427; 39374</t>
+          <t>19428; 40000</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11403; 30104</t>
+          <t>10849; 29414</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23349; 37483</t>
+          <t>25535; 41645</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17884; 36287</t>
+          <t>17826; 37363</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19427; 39374</t>
+          <t>19428; 40000</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11403; 30104</t>
+          <t>10849; 29414</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23206; 37112</t>
+          <t>25136; 41381</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24527</t>
+          <t>26210</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>59247</t>
+          <t>64884</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>83774</t>
+          <t>91095</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8978; 22788</t>
+          <t>8993; 22591</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12907; 30208</t>
+          <t>12905; 30593</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11444; 26023</t>
+          <t>11091; 25643</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18141; 32050</t>
+          <t>18885; 34084</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38499; 63705</t>
+          <t>38243; 63953</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33064; 60575</t>
+          <t>34265; 59730</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29514; 57463</t>
+          <t>29966; 56150</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>49767; 70622</t>
+          <t>53219; 75055</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>52046; 79541</t>
+          <t>52795; 80466</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52430; 82146</t>
+          <t>52079; 85030</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45109; 74663</t>
+          <t>44829; 76956</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>72159; 95296</t>
+          <t>78026; 105290</t>
         </is>
       </c>
     </row>
